--- a/artfynd/A 59967-2024 artfynd.xlsx
+++ b/artfynd/A 59967-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122210829</v>
       </c>
       <c r="B2" t="n">
-        <v>100414</v>
+        <v>100424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 59967-2024 artfynd.xlsx
+++ b/artfynd/A 59967-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122210829</v>
       </c>
       <c r="B2" t="n">
-        <v>100424</v>
+        <v>100436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 59967-2024 artfynd.xlsx
+++ b/artfynd/A 59967-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122210829</v>
       </c>
       <c r="B2" t="n">
-        <v>100436</v>
+        <v>100441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 59967-2024 artfynd.xlsx
+++ b/artfynd/A 59967-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122210829</v>
       </c>
       <c r="B2" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>1365</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 59967-2024 artfynd.xlsx
+++ b/artfynd/A 59967-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122210829</v>
       </c>
       <c r="B2" t="n">
-        <v>100450</v>
+        <v>100463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>1365</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 59967-2024 artfynd.xlsx
+++ b/artfynd/A 59967-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122210829</v>
       </c>
       <c r="B2" t="n">
-        <v>100463</v>
+        <v>100476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 59967-2024 artfynd.xlsx
+++ b/artfynd/A 59967-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122210829</v>
       </c>
       <c r="B2" t="n">
-        <v>100476</v>
+        <v>100479</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
